--- a/artfynd/A 33340-2025 artfynd.xlsx
+++ b/artfynd/A 33340-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126016933</v>
       </c>
       <c r="B2" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126016931</v>
       </c>
       <c r="B3" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126016934</v>
       </c>
       <c r="B4" t="n">
-        <v>90280</v>
+        <v>90283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33340-2025 artfynd.xlsx
+++ b/artfynd/A 33340-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126016933</v>
+        <v>126016927</v>
       </c>
       <c r="B2" t="n">
-        <v>79569</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>678341</v>
+        <v>678371</v>
       </c>
       <c r="R2" t="n">
-        <v>7128599</v>
+        <v>7128811</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126016931</v>
+        <v>126016934</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678354</v>
+        <v>678365</v>
       </c>
       <c r="R3" t="n">
-        <v>7128664</v>
+        <v>7128545</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126016934</v>
+        <v>126016928</v>
       </c>
       <c r="B4" t="n">
-        <v>90283</v>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678365</v>
+        <v>678499</v>
       </c>
       <c r="R4" t="n">
-        <v>7128545</v>
+        <v>7128863</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -990,6 +990,430 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126016929</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>678500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7128861</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126016926</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>678382</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7128818</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126016931</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>678354</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7128664</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126016933</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vargträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>678341</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7128599</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33340-2025 artfynd.xlsx
+++ b/artfynd/A 33340-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016927</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016934</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016928</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016929</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016926</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016931</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016933</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>